--- a/output/roomself_excel/11557.xlsx
+++ b/output/roomself_excel/11557.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:P3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,62 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_4</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_4</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_4</t>
         </is>
       </c>
     </row>
@@ -475,11 +525,49 @@
       <c r="D2" t="n">
         <v>5408</v>
       </c>
-      <c r="E2" t="n">
-        <v>670</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>478</v>
+        <v>616</v>
+      </c>
+      <c r="G2" t="n">
+        <v>16</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>404</v>
+      </c>
+      <c r="J2" t="n">
+        <v>16</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>444</v>
+      </c>
+      <c r="M2" t="n">
+        <v>38</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>376</v>
+      </c>
+      <c r="P2" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="3">
@@ -497,12 +585,26 @@
       <c r="D3" t="n">
         <v>1244</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
         <v>191</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>18</v>
       </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/roomself_excel/11557.xlsx
+++ b/output/roomself_excel/11557.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rooms" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P3"/>
+  <dimension ref="A1:X3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +509,46 @@
           <t>ExtWallWidth_4</t>
         </is>
       </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_1</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_1</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_1</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_1</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_2</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_2</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_2</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_2</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -567,6 +607,38 @@
         <v>376</v>
       </c>
       <c r="P2" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
+        <v>400</v>
+      </c>
+      <c r="T2" t="n">
+        <v>38</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="W2" t="n">
+        <v>84</v>
+      </c>
+      <c r="X2" t="n">
         <v>18</v>
       </c>
     </row>
@@ -605,6 +677,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
